--- a/artfynd/A 10471-2024 artfynd.xlsx
+++ b/artfynd/A 10471-2024 artfynd.xlsx
@@ -776,6 +776,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 10471-2024 artfynd.xlsx
+++ b/artfynd/A 10471-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118801218</v>
       </c>
       <c r="B2" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
